--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -4,7 +4,8 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <sheets>
     <sheet name="Customer" sheetId="1" r:id="rId1"/>
-    <sheet name="Ticket" sheetId="2" r:id="rId2"/>
+    <sheet name="Staff" sheetId="2" r:id="rId2"/>
+    <sheet name="Ticket" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,42 +417,151 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>C-1789530864600</v>
+        <v>C-1789539845003</v>
       </c>
       <c r="B2" t="str">
-        <v>corn</v>
+        <v>w</v>
       </c>
       <c r="C2" t="str">
-        <v>corn@gmail.com</v>
+        <v>w@gmail.com</v>
       </c>
       <c r="D2" t="str">
-        <v>corn</v>
+        <v>w</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>C-1789531353772</v>
+        <v>C-1789540251755</v>
       </c>
       <c r="B3" t="str">
-        <v>hu</v>
+        <v>hhhh</v>
       </c>
       <c r="C3" t="str">
+        <v>hh@123.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>C-1789540522087</v>
+      </c>
+      <c r="B4" t="str">
+        <v>hi</v>
+      </c>
+      <c r="C4" t="str">
         <v>hi@gmail.com</v>
       </c>
-      <c r="D3" t="str">
-        <v>1</v>
+      <c r="D4" t="str">
+        <v>hi</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Staff ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Password</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Role</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Department</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>S-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="C2" t="str">
+        <v>itadmin@company.com</v>
+      </c>
+      <c r="D2" t="str">
+        <v>admin123</v>
+      </c>
+      <c r="E2" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Information Technology</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>S-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>John</v>
+      </c>
+      <c r="C3" t="str">
+        <v>john@gmail.com</v>
+      </c>
+      <c r="D3" t="str">
+        <v>john123</v>
+      </c>
+      <c r="E3" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Information Technology</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>S-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Taro</v>
+      </c>
+      <c r="C4" t="str">
+        <v>taro@gmail.com</v>
+      </c>
+      <c r="D4" t="str">
+        <v>taro123</v>
+      </c>
+      <c r="E4" t="str">
+        <v>IT Support Staff</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Information Technology</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1"/>
+    <hyperlink ref="C4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M3"/>
   <sheetData>
     <row r="1">
@@ -518,7 +628,7 @@
         <v>Open</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Taro</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -578,6 +688,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
   </ignoredErrors>

--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,6 +414,9 @@
       <c r="D1" t="str">
         <v>Password</v>
       </c>
+      <c r="E1" t="str">
+        <v>Credits</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -428,6 +431,9 @@
       <c r="D2" t="str">
         <v>w</v>
       </c>
+      <c r="E2">
+        <v>10000</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -442,6 +448,9 @@
       <c r="D3" t="str">
         <v>12</v>
       </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -456,10 +465,14 @@
       <c r="D4" t="str">
         <v>hi</v>
       </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -562,7 +575,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,28 +620,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>T-1789531922103</v>
+        <v>T-1789549665787</v>
       </c>
       <c r="B2" t="str">
-        <v>C-1789530864600</v>
+        <v>C-1789539845003</v>
       </c>
       <c r="C2" t="str">
-        <v>corn</v>
+        <v>w</v>
       </c>
       <c r="D2" t="str">
-        <v>corn@gmail.com</v>
+        <v>w@gmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>e</v>
+        <v>w</v>
       </c>
       <c r="F2" t="str">
-        <v>Phone Support</v>
+        <v>Email Support</v>
       </c>
       <c r="G2" t="str">
         <v>Open</v>
       </c>
       <c r="H2" t="str">
-        <v>Taro</v>
+        <v/>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -640,7 +653,7 @@
         <v>Pending</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-09-16T04:12:02.103Z</v>
+        <v>2026-09-16T09:07:45.787Z</v>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -648,22 +661,22 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>T-1789532243142</v>
+        <v>T-1789551066051</v>
       </c>
       <c r="B3" t="str">
-        <v>C-1789531353772</v>
+        <v>C-1789539845003</v>
       </c>
       <c r="C3" t="str">
-        <v>hu</v>
+        <v>w</v>
       </c>
       <c r="D3" t="str">
-        <v>hi@gmail.com</v>
+        <v>w@gmail.com</v>
       </c>
       <c r="E3" t="str">
-        <v>e</v>
+        <v>w</v>
       </c>
       <c r="F3" t="str">
-        <v>Remote Support</v>
+        <v>On-site Support</v>
       </c>
       <c r="G3" t="str">
         <v>Open</v>
@@ -672,25 +685,65 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>2026-09-16</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>04:00</v>
       </c>
       <c r="K3" t="str">
         <v>Pending</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-09-16T04:17:23.142Z</v>
+        <v>2026-09-16T09:31:06.051Z</v>
       </c>
       <c r="M3" t="str">
         <v/>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>T-1789551317217</v>
+      </c>
+      <c r="B4" t="str">
+        <v>C-1789540522087</v>
+      </c>
+      <c r="C4" t="str">
+        <v>hi</v>
+      </c>
+      <c r="D4" t="str">
+        <v>hi@gmail.com</v>
+      </c>
+      <c r="E4" t="str">
+        <v>hi</v>
+      </c>
+      <c r="F4" t="str">
+        <v>On-site Support</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Open</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-09-16</v>
+      </c>
+      <c r="J4" t="str">
+        <v>14:22</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L4" t="str">
+        <v>2026-09-16T09:35:17.217Z</v>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -432,7 +432,7 @@
         <v>w</v>
       </c>
       <c r="E2">
-        <v>10000</v>
+        <v>9997.5</v>
       </c>
     </row>
     <row r="3">
@@ -470,7 +470,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
@@ -575,7 +574,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -617,6 +616,9 @@
       <c r="M1" t="str">
         <v>Service Result</v>
       </c>
+      <c r="N1" t="str">
+        <v>Appointment Duration</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -741,9 +743,53 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>T-1789612465526</v>
+      </c>
+      <c r="B5" t="str">
+        <v>C-1789539845003</v>
+      </c>
+      <c r="C5" t="str">
+        <v>w</v>
+      </c>
+      <c r="D5" t="str">
+        <v>w@gmail.com</v>
+      </c>
+      <c r="E5" t="str">
+        <v>w</v>
+      </c>
+      <c r="F5" t="str">
+        <v>On-site Support</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Open</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="J5" t="str">
+        <v>14:09</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-09-17T02:34:25.526Z</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -574,7 +574,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -622,7 +622,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>T-1789549665787</v>
+        <v>T-1789612465526</v>
       </c>
       <c r="B2" t="str">
         <v>C-1789539845003</v>
@@ -637,7 +637,7 @@
         <v>w</v>
       </c>
       <c r="F2" t="str">
-        <v>Email Support</v>
+        <v>On-site Support</v>
       </c>
       <c r="G2" t="str">
         <v>Open</v>
@@ -646,39 +646,42 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>2026-09-17</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>14:09</v>
       </c>
       <c r="K2" t="str">
         <v>Pending</v>
       </c>
       <c r="L2" t="str">
-        <v>2026-09-16T09:07:45.787Z</v>
+        <v>2026-09-17T02:34:25.526Z</v>
       </c>
       <c r="M2" t="str">
         <v/>
+      </c>
+      <c r="N2">
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>T-1789551066051</v>
+        <v>T-1789629426548</v>
       </c>
       <c r="B3" t="str">
-        <v>C-1789539845003</v>
+        <v/>
       </c>
       <c r="C3" t="str">
-        <v>w</v>
+        <v>pokijh</v>
       </c>
       <c r="D3" t="str">
-        <v>w@gmail.com</v>
+        <v>dorothy@600gmail.com</v>
       </c>
       <c r="E3" t="str">
-        <v>w</v>
+        <v>ojihg</v>
       </c>
       <c r="F3" t="str">
-        <v>On-site Support</v>
+        <v>Phone Support</v>
       </c>
       <c r="G3" t="str">
         <v>Open</v>
@@ -687,16 +690,16 @@
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>2026-09-16</v>
+        <v/>
       </c>
       <c r="J3" t="str">
-        <v>04:00</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v>Pending</v>
       </c>
       <c r="L3" t="str">
-        <v>2026-09-16T09:31:06.051Z</v>
+        <v>2026-09-17T07:17:06.548Z</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -704,22 +707,22 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>T-1789551317217</v>
+        <v>T-1789951228874</v>
       </c>
       <c r="B4" t="str">
-        <v>C-1789540522087</v>
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>hi</v>
+        <v>tom</v>
       </c>
       <c r="D4" t="str">
-        <v>hi@gmail.com</v>
+        <v>tom@gmail.com</v>
       </c>
       <c r="E4" t="str">
-        <v>hi</v>
+        <v>something wrong</v>
       </c>
       <c r="F4" t="str">
-        <v>On-site Support</v>
+        <v>Phone Support</v>
       </c>
       <c r="G4" t="str">
         <v>Open</v>
@@ -728,68 +731,24 @@
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>2026-09-16</v>
+        <v/>
       </c>
       <c r="J4" t="str">
-        <v>14:22</v>
+        <v/>
       </c>
       <c r="K4" t="str">
         <v>Pending</v>
       </c>
       <c r="L4" t="str">
-        <v>2026-09-16T09:35:17.217Z</v>
+        <v>2026-09-21T00:40:28.874Z</v>
       </c>
       <c r="M4" t="str">
         <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>T-1789612465526</v>
-      </c>
-      <c r="B5" t="str">
-        <v>C-1789539845003</v>
-      </c>
-      <c r="C5" t="str">
-        <v>w</v>
-      </c>
-      <c r="D5" t="str">
-        <v>w@gmail.com</v>
-      </c>
-      <c r="E5" t="str">
-        <v>w</v>
-      </c>
-      <c r="F5" t="str">
-        <v>On-site Support</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Open</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>2026-09-17</v>
-      </c>
-      <c r="J5" t="str">
-        <v>14:09</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Pending</v>
-      </c>
-      <c r="L5" t="str">
-        <v>2026-09-17T02:34:25.526Z</v>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
-      <c r="N5">
-        <v>2.5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -640,10 +640,10 @@
         <v>On-site Support</v>
       </c>
       <c r="G2" t="str">
-        <v>Open</v>
+        <v>Closed</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>John</v>
       </c>
       <c r="I2" t="str">
         <v>2026-09-17</v>
@@ -652,13 +652,13 @@
         <v>14:09</v>
       </c>
       <c r="K2" t="str">
-        <v>Pending</v>
+        <v>Confirmed</v>
       </c>
       <c r="L2" t="str">
         <v>2026-09-17T02:34:25.526Z</v>
       </c>
       <c r="M2" t="str">
-        <v/>
+        <v>Resolved by test</v>
       </c>
       <c r="N2">
         <v>2.5</v>

--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -640,10 +640,10 @@
         <v>On-site Support</v>
       </c>
       <c r="G2" t="str">
-        <v>Closed</v>
+        <v>In Progress</v>
       </c>
       <c r="H2" t="str">
-        <v>John</v>
+        <v/>
       </c>
       <c r="I2" t="str">
         <v>2026-09-17</v>
@@ -652,13 +652,13 @@
         <v>14:09</v>
       </c>
       <c r="K2" t="str">
-        <v>Confirmed</v>
+        <v>Pending</v>
       </c>
       <c r="L2" t="str">
         <v>2026-09-17T02:34:25.526Z</v>
       </c>
       <c r="M2" t="str">
-        <v>Resolved by test</v>
+        <v/>
       </c>
       <c r="N2">
         <v>2.5</v>

--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -574,7 +574,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -746,9 +746,53 @@
         <v/>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>T-1789963309340</v>
+      </c>
+      <c r="B5" t="str">
+        <v/>
+      </c>
+      <c r="C5" t="str">
+        <v>josiah wimbleton</v>
+      </c>
+      <c r="D5" t="str">
+        <v>ya@rawr.waow</v>
+      </c>
+      <c r="E5" t="str">
+        <v>hel</v>
+      </c>
+      <c r="F5" t="str">
+        <v>On-site Support</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Open</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="J5" t="str">
+        <v>03:00</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L5" t="str">
+        <v>2026-09-21T04:01:49.340Z</v>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Database/database.xlsx
+++ b/Database/database.xlsx
@@ -714,7 +714,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -974,9 +974,56 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>T-1789984570988</v>
+      </c>
+      <c r="B7" t="str">
+        <v>C-0000000000004</v>
+      </c>
+      <c r="C7" t="str">
+        <v>josiah wimbleton</v>
+      </c>
+      <c r="D7" t="str">
+        <v>ya@rawr.waow</v>
+      </c>
+      <c r="E7" t="str">
+        <v>helpppppppp</v>
+      </c>
+      <c r="F7" t="str">
+        <v>On-site Support</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Open</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>2026-09-30</v>
+      </c>
+      <c r="J7" t="str">
+        <v>03:00</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Pending</v>
+      </c>
+      <c r="L7" t="str">
+        <v>2026-09-21T09:56:10.988Z</v>
+      </c>
+      <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7">
+        <v>17</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Project</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O7"/>
   </ignoredErrors>
 </worksheet>
 </file>